--- a/exports/golf_prices_20260426.xlsx
+++ b/exports/golf_prices_20260426.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:43</t>
+          <t>2026-04-26 21:17:58</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:43</t>
+          <t>2026-04-26 21:17:58</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -648,7 +648,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:44</t>
+          <t>2026-04-26 21:18:00</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -719,7 +719,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:44</t>
+          <t>2026-04-26 21:18:00</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -790,7 +790,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:46</t>
+          <t>2026-04-26 21:18:02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:46</t>
+          <t>2026-04-26 21:18:02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -932,7 +932,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:48</t>
+          <t>2026-04-26 21:18:04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:48</t>
+          <t>2026-04-26 21:18:04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:50</t>
+          <t>2026-04-26 21:18:05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1145,7 +1145,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:50</t>
+          <t>2026-04-26 21:18:05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:52</t>
+          <t>2026-04-26 21:18:07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1287,7 +1287,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:52</t>
+          <t>2026-04-26 21:18:07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1358,7 +1358,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:54</t>
+          <t>2026-04-26 21:18:09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1429,7 +1429,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:54</t>
+          <t>2026-04-26 21:18:09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:56</t>
+          <t>2026-04-26 21:18:11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:56</t>
+          <t>2026-04-26 21:18:11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1642,7 +1642,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:58</t>
+          <t>2026-04-26 21:18:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1713,7 +1713,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-26 00:27:58</t>
+          <t>2026-04-26 21:18:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1784,7 +1784,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:00</t>
+          <t>2026-04-26 21:18:15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1855,7 +1855,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:00</t>
+          <t>2026-04-26 21:18:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1926,7 +1926,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:02</t>
+          <t>2026-04-26 21:18:17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1997,7 +1997,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:02</t>
+          <t>2026-04-26 21:18:17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2068,7 +2068,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:04</t>
+          <t>2026-04-26 21:18:19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:04</t>
+          <t>2026-04-26 21:18:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2210,7 +2210,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:06</t>
+          <t>2026-04-26 21:18:21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2281,7 +2281,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:06</t>
+          <t>2026-04-26 21:18:21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2352,7 +2352,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:08</t>
+          <t>2026-04-26 21:18:23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2423,7 +2423,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:08</t>
+          <t>2026-04-26 21:18:23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2494,7 +2494,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:10</t>
+          <t>2026-04-26 21:18:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2565,7 +2565,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:10</t>
+          <t>2026-04-26 21:18:25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2636,7 +2636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:11</t>
+          <t>2026-04-26 21:18:27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2707,7 +2707,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:11</t>
+          <t>2026-04-26 21:18:27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2778,7 +2778,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:13</t>
+          <t>2026-04-26 21:18:29</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2849,7 +2849,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:13</t>
+          <t>2026-04-26 21:18:29</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2920,7 +2920,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:15</t>
+          <t>2026-04-26 21:18:31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2991,7 +2991,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:15</t>
+          <t>2026-04-26 21:18:31</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3062,7 +3062,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:17</t>
+          <t>2026-04-26 21:18:33</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3133,7 +3133,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:17</t>
+          <t>2026-04-26 21:18:33</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3204,7 +3204,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:19</t>
+          <t>2026-04-26 21:18:35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3254,7 +3254,7 @@
         <v>161427</v>
       </c>
       <c r="L40" t="n">
-        <v>109.25</v>
+        <v>109.24</v>
       </c>
       <c r="M40" t="b">
         <v>1</v>
@@ -3275,7 +3275,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:19</t>
+          <t>2026-04-26 21:18:35</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3325,7 +3325,7 @@
         <v>161427</v>
       </c>
       <c r="L41" t="n">
-        <v>109.25</v>
+        <v>109.24</v>
       </c>
       <c r="M41" t="b">
         <v>1</v>
@@ -3346,7 +3346,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:21</t>
+          <t>2026-04-26 21:18:37</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3396,7 +3396,7 @@
         <v>161427</v>
       </c>
       <c r="L42" t="n">
-        <v>109.25</v>
+        <v>109.24</v>
       </c>
       <c r="M42" t="b">
         <v>1</v>
@@ -3417,7 +3417,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:21</t>
+          <t>2026-04-26 21:18:37</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3467,7 +3467,7 @@
         <v>161427</v>
       </c>
       <c r="L43" t="n">
-        <v>109.25</v>
+        <v>109.24</v>
       </c>
       <c r="M43" t="b">
         <v>1</v>
@@ -3488,7 +3488,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:23</t>
+          <t>2026-04-26 21:18:39</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3559,7 +3559,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:23</t>
+          <t>2026-04-26 21:18:39</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3630,7 +3630,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:25</t>
+          <t>2026-04-26 21:18:40</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3701,7 +3701,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:25</t>
+          <t>2026-04-26 21:18:40</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3772,7 +3772,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:26</t>
+          <t>2026-04-26 21:18:42</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3843,7 +3843,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:26</t>
+          <t>2026-04-26 21:18:42</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3914,7 +3914,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:28</t>
+          <t>2026-04-26 21:18:44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3985,7 +3985,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:28</t>
+          <t>2026-04-26 21:18:44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4056,7 +4056,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:30</t>
+          <t>2026-04-26 21:18:46</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4127,7 +4127,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:30</t>
+          <t>2026-04-26 21:18:46</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4198,7 +4198,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:32</t>
+          <t>2026-04-26 21:18:48</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4248,7 +4248,7 @@
         <v>161427</v>
       </c>
       <c r="L54" t="n">
-        <v>109.25</v>
+        <v>109.24</v>
       </c>
       <c r="M54" t="b">
         <v>1</v>
@@ -4269,7 +4269,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:32</t>
+          <t>2026-04-26 21:18:48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4319,7 +4319,7 @@
         <v>161427</v>
       </c>
       <c r="L55" t="n">
-        <v>109.25</v>
+        <v>109.24</v>
       </c>
       <c r="M55" t="b">
         <v>1</v>
@@ -4340,7 +4340,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:34</t>
+          <t>2026-04-26 21:18:50</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4390,7 +4390,7 @@
         <v>161427</v>
       </c>
       <c r="L56" t="n">
-        <v>109.25</v>
+        <v>109.24</v>
       </c>
       <c r="M56" t="b">
         <v>1</v>
@@ -4411,7 +4411,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:34</t>
+          <t>2026-04-26 21:18:50</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4461,7 +4461,7 @@
         <v>161427</v>
       </c>
       <c r="L57" t="n">
-        <v>109.25</v>
+        <v>109.24</v>
       </c>
       <c r="M57" t="b">
         <v>1</v>
@@ -4482,7 +4482,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:36</t>
+          <t>2026-04-26 21:18:52</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4532,7 +4532,7 @@
         <v>167519</v>
       </c>
       <c r="L58" t="n">
-        <v>113.37</v>
+        <v>113.36</v>
       </c>
       <c r="M58" t="b">
         <v>1</v>
@@ -4553,7 +4553,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:36</t>
+          <t>2026-04-26 21:18:52</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4603,7 +4603,7 @@
         <v>167519</v>
       </c>
       <c r="L59" t="n">
-        <v>113.37</v>
+        <v>113.36</v>
       </c>
       <c r="M59" t="b">
         <v>1</v>
@@ -4624,7 +4624,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:38</t>
+          <t>2026-04-26 21:18:54</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4695,7 +4695,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:38</t>
+          <t>2026-04-26 21:18:54</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4766,7 +4766,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:39</t>
+          <t>2026-04-26 21:18:56</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4837,7 +4837,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:39</t>
+          <t>2026-04-26 21:18:56</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4908,7 +4908,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:41</t>
+          <t>2026-04-26 21:18:58</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4958,7 +4958,7 @@
         <v>167519</v>
       </c>
       <c r="L64" t="n">
-        <v>113.37</v>
+        <v>113.36</v>
       </c>
       <c r="M64" t="b">
         <v>1</v>
@@ -4979,7 +4979,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:41</t>
+          <t>2026-04-26 21:18:58</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5029,7 +5029,7 @@
         <v>167519</v>
       </c>
       <c r="L65" t="n">
-        <v>113.37</v>
+        <v>113.36</v>
       </c>
       <c r="M65" t="b">
         <v>1</v>
@@ -5050,7 +5050,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:43</t>
+          <t>2026-04-26 21:19:00</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5100,7 +5100,7 @@
         <v>167519</v>
       </c>
       <c r="L66" t="n">
-        <v>113.37</v>
+        <v>113.36</v>
       </c>
       <c r="M66" t="b">
         <v>1</v>
@@ -5121,7 +5121,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:43</t>
+          <t>2026-04-26 21:19:00</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5171,7 +5171,7 @@
         <v>167519</v>
       </c>
       <c r="L67" t="n">
-        <v>113.37</v>
+        <v>113.36</v>
       </c>
       <c r="M67" t="b">
         <v>1</v>
@@ -5192,7 +5192,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:45</t>
+          <t>2026-04-26 21:19:02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5242,7 +5242,7 @@
         <v>167519</v>
       </c>
       <c r="L68" t="n">
-        <v>113.37</v>
+        <v>113.36</v>
       </c>
       <c r="M68" t="b">
         <v>1</v>
@@ -5263,7 +5263,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:45</t>
+          <t>2026-04-26 21:19:02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5313,7 +5313,7 @@
         <v>167519</v>
       </c>
       <c r="L69" t="n">
-        <v>113.37</v>
+        <v>113.36</v>
       </c>
       <c r="M69" t="b">
         <v>1</v>
@@ -5334,7 +5334,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:47</t>
+          <t>2026-04-26 21:19:04</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5384,7 +5384,7 @@
         <v>167519</v>
       </c>
       <c r="L70" t="n">
-        <v>113.37</v>
+        <v>113.36</v>
       </c>
       <c r="M70" t="b">
         <v>1</v>
@@ -5405,7 +5405,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:47</t>
+          <t>2026-04-26 21:19:04</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5455,7 +5455,7 @@
         <v>167519</v>
       </c>
       <c r="L71" t="n">
-        <v>113.37</v>
+        <v>113.36</v>
       </c>
       <c r="M71" t="b">
         <v>1</v>
@@ -5476,7 +5476,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:49</t>
+          <t>2026-04-26 21:19:06</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5547,7 +5547,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:49</t>
+          <t>2026-04-26 21:19:06</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5618,7 +5618,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:51</t>
+          <t>2026-04-26 21:19:07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5689,7 +5689,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:51</t>
+          <t>2026-04-26 21:19:07</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5760,7 +5760,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:53</t>
+          <t>2026-04-26 21:19:09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5831,7 +5831,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:53</t>
+          <t>2026-04-26 21:19:09</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5902,7 +5902,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:55</t>
+          <t>2026-04-26 21:19:11</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5973,7 +5973,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:55</t>
+          <t>2026-04-26 21:19:11</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6044,7 +6044,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:56</t>
+          <t>2026-04-26 21:19:13</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6115,7 +6115,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:56</t>
+          <t>2026-04-26 21:19:13</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6186,7 +6186,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:58</t>
+          <t>2026-04-26 21:19:15</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6236,7 +6236,7 @@
         <v>167519</v>
       </c>
       <c r="L82" t="n">
-        <v>113.37</v>
+        <v>113.36</v>
       </c>
       <c r="M82" t="b">
         <v>1</v>
@@ -6257,7 +6257,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-04-26 00:28:58</t>
+          <t>2026-04-26 21:19:15</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6307,7 +6307,7 @@
         <v>167519</v>
       </c>
       <c r="L83" t="n">
-        <v>113.37</v>
+        <v>113.36</v>
       </c>
       <c r="M83" t="b">
         <v>1</v>
@@ -6328,7 +6328,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:00</t>
+          <t>2026-04-26 21:19:17</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6378,7 +6378,7 @@
         <v>167519</v>
       </c>
       <c r="L84" t="n">
-        <v>113.37</v>
+        <v>113.36</v>
       </c>
       <c r="M84" t="b">
         <v>1</v>
@@ -6399,7 +6399,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:00</t>
+          <t>2026-04-26 21:19:17</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6449,7 +6449,7 @@
         <v>167519</v>
       </c>
       <c r="L85" t="n">
-        <v>113.37</v>
+        <v>113.36</v>
       </c>
       <c r="M85" t="b">
         <v>1</v>
@@ -6470,7 +6470,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:02</t>
+          <t>2026-04-26 21:19:19</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6541,7 +6541,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:02</t>
+          <t>2026-04-26 21:19:19</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6612,7 +6612,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:04</t>
+          <t>2026-04-26 21:19:21</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6662,7 +6662,7 @@
         <v>137061</v>
       </c>
       <c r="L88" t="n">
-        <v>92.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="M88" t="b">
         <v>1</v>
@@ -6683,7 +6683,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:04</t>
+          <t>2026-04-26 21:19:21</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6733,7 +6733,7 @@
         <v>137061</v>
       </c>
       <c r="L89" t="n">
-        <v>92.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="M89" t="b">
         <v>1</v>
@@ -6754,7 +6754,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:06</t>
+          <t>2026-04-26 21:19:23</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -6804,7 +6804,7 @@
         <v>137061</v>
       </c>
       <c r="L90" t="n">
-        <v>92.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="M90" t="b">
         <v>1</v>
@@ -6825,7 +6825,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:06</t>
+          <t>2026-04-26 21:19:23</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6875,7 +6875,7 @@
         <v>137061</v>
       </c>
       <c r="L91" t="n">
-        <v>92.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="M91" t="b">
         <v>1</v>
@@ -6896,7 +6896,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:08</t>
+          <t>2026-04-26 21:19:25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6967,7 +6967,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:08</t>
+          <t>2026-04-26 21:19:25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7038,7 +7038,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:10</t>
+          <t>2026-04-26 21:19:27</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -7088,7 +7088,7 @@
         <v>216251</v>
       </c>
       <c r="L94" t="n">
-        <v>146.35</v>
+        <v>146.34</v>
       </c>
       <c r="M94" t="b">
         <v>1</v>
@@ -7109,7 +7109,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:10</t>
+          <t>2026-04-26 21:19:27</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -7159,7 +7159,7 @@
         <v>216251</v>
       </c>
       <c r="L95" t="n">
-        <v>146.35</v>
+        <v>146.34</v>
       </c>
       <c r="M95" t="b">
         <v>1</v>
@@ -7180,7 +7180,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:12</t>
+          <t>2026-04-26 21:19:29</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7251,7 +7251,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:12</t>
+          <t>2026-04-26 21:19:29</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7322,7 +7322,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:14</t>
+          <t>2026-04-26 21:19:31</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7393,7 +7393,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:14</t>
+          <t>2026-04-26 21:19:31</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7464,7 +7464,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:15</t>
+          <t>2026-04-26 21:19:33</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -7514,7 +7514,7 @@
         <v>137061</v>
       </c>
       <c r="L100" t="n">
-        <v>92.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="M100" t="b">
         <v>1</v>
@@ -7535,7 +7535,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:15</t>
+          <t>2026-04-26 21:19:33</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -7585,7 +7585,7 @@
         <v>137061</v>
       </c>
       <c r="L101" t="n">
-        <v>92.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="M101" t="b">
         <v>1</v>
@@ -7606,7 +7606,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:17</t>
+          <t>2026-04-26 21:19:34</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -7656,7 +7656,7 @@
         <v>137061</v>
       </c>
       <c r="L102" t="n">
-        <v>92.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="M102" t="b">
         <v>1</v>
@@ -7677,7 +7677,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:17</t>
+          <t>2026-04-26 21:19:34</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -7727,7 +7727,7 @@
         <v>137061</v>
       </c>
       <c r="L103" t="n">
-        <v>92.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="M103" t="b">
         <v>1</v>
@@ -7748,7 +7748,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:19</t>
+          <t>2026-04-26 21:19:36</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7798,7 +7798,7 @@
         <v>137061</v>
       </c>
       <c r="L104" t="n">
-        <v>92.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="M104" t="b">
         <v>1</v>
@@ -7819,7 +7819,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:19</t>
+          <t>2026-04-26 21:19:36</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7869,7 +7869,7 @@
         <v>137061</v>
       </c>
       <c r="L105" t="n">
-        <v>92.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="M105" t="b">
         <v>1</v>
@@ -7890,7 +7890,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:21</t>
+          <t>2026-04-26 21:19:38</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -7940,7 +7940,7 @@
         <v>137061</v>
       </c>
       <c r="L106" t="n">
-        <v>92.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="M106" t="b">
         <v>1</v>
@@ -7961,7 +7961,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:21</t>
+          <t>2026-04-26 21:19:38</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -8011,7 +8011,7 @@
         <v>137061</v>
       </c>
       <c r="L107" t="n">
-        <v>92.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="M107" t="b">
         <v>1</v>
@@ -8032,7 +8032,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:23</t>
+          <t>2026-04-26 21:19:40</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -8082,7 +8082,7 @@
         <v>137061</v>
       </c>
       <c r="L108" t="n">
-        <v>92.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="M108" t="b">
         <v>1</v>
@@ -8103,7 +8103,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:23</t>
+          <t>2026-04-26 21:19:40</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -8153,7 +8153,7 @@
         <v>137061</v>
       </c>
       <c r="L109" t="n">
-        <v>92.76000000000001</v>
+        <v>92.75</v>
       </c>
       <c r="M109" t="b">
         <v>1</v>
@@ -8174,7 +8174,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:25</t>
+          <t>2026-04-26 21:19:42</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -8245,7 +8245,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:25</t>
+          <t>2026-04-26 21:19:42</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -8316,7 +8316,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:27</t>
+          <t>2026-04-26 21:19:44</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -8387,7 +8387,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:27</t>
+          <t>2026-04-26 21:19:44</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -8458,7 +8458,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:28</t>
+          <t>2026-04-26 21:19:46</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -8508,7 +8508,7 @@
         <v>278119</v>
       </c>
       <c r="L114" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M114" t="b">
         <v>1</v>
@@ -8529,7 +8529,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:28</t>
+          <t>2026-04-26 21:19:46</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -8579,7 +8579,7 @@
         <v>278119</v>
       </c>
       <c r="L115" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M115" t="b">
         <v>1</v>
@@ -8600,7 +8600,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:30</t>
+          <t>2026-04-26 21:19:48</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -8650,7 +8650,7 @@
         <v>278119</v>
       </c>
       <c r="L116" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M116" t="b">
         <v>1</v>
@@ -8671,7 +8671,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:30</t>
+          <t>2026-04-26 21:19:48</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8721,7 +8721,7 @@
         <v>278119</v>
       </c>
       <c r="L117" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M117" t="b">
         <v>1</v>
@@ -8742,7 +8742,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:32</t>
+          <t>2026-04-26 21:19:50</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8792,7 +8792,7 @@
         <v>278119</v>
       </c>
       <c r="L118" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M118" t="b">
         <v>1</v>
@@ -8813,7 +8813,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:32</t>
+          <t>2026-04-26 21:19:50</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -8863,7 +8863,7 @@
         <v>278119</v>
       </c>
       <c r="L119" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M119" t="b">
         <v>1</v>
@@ -8884,7 +8884,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:34</t>
+          <t>2026-04-26 21:19:52</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -8934,7 +8934,7 @@
         <v>278119</v>
       </c>
       <c r="L120" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M120" t="b">
         <v>1</v>
@@ -8955,7 +8955,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:34</t>
+          <t>2026-04-26 21:19:52</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9005,7 +9005,7 @@
         <v>278119</v>
       </c>
       <c r="L121" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M121" t="b">
         <v>1</v>
@@ -9026,7 +9026,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:36</t>
+          <t>2026-04-26 21:19:54</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9076,7 +9076,7 @@
         <v>278119</v>
       </c>
       <c r="L122" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M122" t="b">
         <v>1</v>
@@ -9097,7 +9097,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:36</t>
+          <t>2026-04-26 21:19:54</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9147,7 +9147,7 @@
         <v>278119</v>
       </c>
       <c r="L123" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M123" t="b">
         <v>1</v>
@@ -9168,7 +9168,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:38</t>
+          <t>2026-04-26 21:19:56</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9218,7 +9218,7 @@
         <v>278119</v>
       </c>
       <c r="L124" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M124" t="b">
         <v>1</v>
@@ -9239,7 +9239,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:38</t>
+          <t>2026-04-26 21:19:56</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9289,7 +9289,7 @@
         <v>278119</v>
       </c>
       <c r="L125" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M125" t="b">
         <v>1</v>
@@ -9310,7 +9310,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:40</t>
+          <t>2026-04-26 21:19:58</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9360,7 +9360,7 @@
         <v>278119</v>
       </c>
       <c r="L126" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M126" t="b">
         <v>1</v>
@@ -9381,7 +9381,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:40</t>
+          <t>2026-04-26 21:19:58</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9431,7 +9431,7 @@
         <v>278119</v>
       </c>
       <c r="L127" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M127" t="b">
         <v>1</v>
@@ -9452,7 +9452,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:42</t>
+          <t>2026-04-26 21:19:59</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9502,7 +9502,7 @@
         <v>278119</v>
       </c>
       <c r="L128" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M128" t="b">
         <v>1</v>
@@ -9523,7 +9523,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:42</t>
+          <t>2026-04-26 21:19:59</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9573,7 +9573,7 @@
         <v>278119</v>
       </c>
       <c r="L129" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M129" t="b">
         <v>1</v>
@@ -9594,7 +9594,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:44</t>
+          <t>2026-04-26 21:20:01</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9644,7 +9644,7 @@
         <v>278119</v>
       </c>
       <c r="L130" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M130" t="b">
         <v>1</v>
@@ -9665,7 +9665,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:44</t>
+          <t>2026-04-26 21:20:01</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9715,7 +9715,7 @@
         <v>278119</v>
       </c>
       <c r="L131" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M131" t="b">
         <v>1</v>
@@ -9736,7 +9736,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:46</t>
+          <t>2026-04-26 21:20:03</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9786,7 +9786,7 @@
         <v>278119</v>
       </c>
       <c r="L132" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M132" t="b">
         <v>1</v>
@@ -9807,7 +9807,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:46</t>
+          <t>2026-04-26 21:20:03</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9857,7 +9857,7 @@
         <v>278119</v>
       </c>
       <c r="L133" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M133" t="b">
         <v>1</v>
@@ -9878,7 +9878,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:48</t>
+          <t>2026-04-26 21:20:06</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9928,7 +9928,7 @@
         <v>278119</v>
       </c>
       <c r="L134" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M134" t="b">
         <v>1</v>
@@ -9949,7 +9949,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:48</t>
+          <t>2026-04-26 21:20:06</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9999,7 +9999,7 @@
         <v>278119</v>
       </c>
       <c r="L135" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M135" t="b">
         <v>1</v>
@@ -10020,7 +10020,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:50</t>
+          <t>2026-04-26 21:20:08</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -10070,7 +10070,7 @@
         <v>278119</v>
       </c>
       <c r="L136" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M136" t="b">
         <v>1</v>
@@ -10091,7 +10091,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:50</t>
+          <t>2026-04-26 21:20:08</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -10141,7 +10141,7 @@
         <v>278119</v>
       </c>
       <c r="L137" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M137" t="b">
         <v>1</v>
@@ -10162,7 +10162,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:51</t>
+          <t>2026-04-26 21:20:09</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -10212,7 +10212,7 @@
         <v>278119</v>
       </c>
       <c r="L138" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M138" t="b">
         <v>1</v>
@@ -10233,7 +10233,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:51</t>
+          <t>2026-04-26 21:20:09</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -10283,7 +10283,7 @@
         <v>278119</v>
       </c>
       <c r="L139" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M139" t="b">
         <v>1</v>
@@ -10304,7 +10304,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:53</t>
+          <t>2026-04-26 21:20:11</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -10354,7 +10354,7 @@
         <v>278119</v>
       </c>
       <c r="L140" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M140" t="b">
         <v>1</v>
@@ -10375,7 +10375,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:53</t>
+          <t>2026-04-26 21:20:11</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -10425,7 +10425,7 @@
         <v>278119</v>
       </c>
       <c r="L141" t="n">
-        <v>188.22</v>
+        <v>188.21</v>
       </c>
       <c r="M141" t="b">
         <v>1</v>
@@ -10446,7 +10446,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:55</t>
+          <t>2026-04-26 21:20:13</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -10517,7 +10517,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:57</t>
+          <t>2026-04-26 21:20:15</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="K143" t="n">
-        <v>300805</v>
+        <v>300816</v>
       </c>
       <c r="L143" t="n">
         <v>203.57</v>
@@ -10588,7 +10588,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:57</t>
+          <t>2026-04-26 21:20:15</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -10659,7 +10659,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:57</t>
+          <t>2026-04-26 21:20:15</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -10730,7 +10730,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:59</t>
+          <t>2026-04-26 21:20:17</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-04-26 00:29:59</t>
+          <t>2026-04-26 21:20:17</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -10872,7 +10872,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:01</t>
+          <t>2026-04-26 21:20:19</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10943,7 +10943,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:01</t>
+          <t>2026-04-26 21:20:19</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11014,7 +11014,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:03</t>
+          <t>2026-04-26 21:20:21</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11085,7 +11085,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:03</t>
+          <t>2026-04-26 21:20:21</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11156,7 +11156,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:05</t>
+          <t>2026-04-26 21:20:23</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11227,7 +11227,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:05</t>
+          <t>2026-04-26 21:20:23</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11298,7 +11298,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:07</t>
+          <t>2026-04-26 21:20:25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11369,7 +11369,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:07</t>
+          <t>2026-04-26 21:20:25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11440,7 +11440,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:09</t>
+          <t>2026-04-26 21:20:27</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11511,7 +11511,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:09</t>
+          <t>2026-04-26 21:20:27</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11582,7 +11582,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:11</t>
+          <t>2026-04-26 21:20:29</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11653,7 +11653,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:11</t>
+          <t>2026-04-26 21:20:29</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11724,7 +11724,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:13</t>
+          <t>2026-04-26 21:20:31</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11795,7 +11795,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:13</t>
+          <t>2026-04-26 21:20:31</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11866,7 +11866,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:14</t>
+          <t>2026-04-26 21:20:33</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11937,7 +11937,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:14</t>
+          <t>2026-04-26 21:20:33</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -12008,7 +12008,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:16</t>
+          <t>2026-04-26 21:20:35</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -12079,7 +12079,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:16</t>
+          <t>2026-04-26 21:20:35</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -12150,7 +12150,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:18</t>
+          <t>2026-04-26 21:20:36</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -12221,7 +12221,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:18</t>
+          <t>2026-04-26 21:20:36</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -12292,7 +12292,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:20</t>
+          <t>2026-04-26 21:20:38</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -12363,7 +12363,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:20</t>
+          <t>2026-04-26 21:20:38</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -12434,7 +12434,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:22</t>
+          <t>2026-04-26 21:20:40</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -12505,7 +12505,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:22</t>
+          <t>2026-04-26 21:20:40</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -12576,7 +12576,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:24</t>
+          <t>2026-04-26 21:20:42</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -12626,7 +12626,7 @@
         <v>204400</v>
       </c>
       <c r="L172" t="n">
-        <v>138.33</v>
+        <v>138.32</v>
       </c>
       <c r="M172" t="b">
         <v>0</v>
@@ -12647,7 +12647,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:24</t>
+          <t>2026-04-26 21:20:42</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -12697,7 +12697,7 @@
         <v>168375</v>
       </c>
       <c r="L173" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M173" t="b">
         <v>1</v>
@@ -12718,7 +12718,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:24</t>
+          <t>2026-04-26 21:20:42</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -12768,7 +12768,7 @@
         <v>168375</v>
       </c>
       <c r="L174" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M174" t="b">
         <v>1</v>
@@ -12789,7 +12789,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:26</t>
+          <t>2026-04-26 21:20:44</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -12839,7 +12839,7 @@
         <v>168375</v>
       </c>
       <c r="L175" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M175" t="b">
         <v>1</v>
@@ -12860,7 +12860,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:26</t>
+          <t>2026-04-26 21:20:44</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -12910,7 +12910,7 @@
         <v>168375</v>
       </c>
       <c r="L176" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M176" t="b">
         <v>1</v>
@@ -12931,7 +12931,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:28</t>
+          <t>2026-04-26 21:20:46</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -12981,7 +12981,7 @@
         <v>168375</v>
       </c>
       <c r="L177" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M177" t="b">
         <v>1</v>
@@ -13002,7 +13002,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:28</t>
+          <t>2026-04-26 21:20:46</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -13052,7 +13052,7 @@
         <v>168375</v>
       </c>
       <c r="L178" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M178" t="b">
         <v>1</v>
@@ -13073,7 +13073,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:29</t>
+          <t>2026-04-26 21:20:48</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -13123,7 +13123,7 @@
         <v>168375</v>
       </c>
       <c r="L179" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M179" t="b">
         <v>1</v>
@@ -13144,7 +13144,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:29</t>
+          <t>2026-04-26 21:20:48</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -13194,7 +13194,7 @@
         <v>168375</v>
       </c>
       <c r="L180" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M180" t="b">
         <v>1</v>
@@ -13215,7 +13215,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:31</t>
+          <t>2026-04-26 21:20:50</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -13265,7 +13265,7 @@
         <v>168375</v>
       </c>
       <c r="L181" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M181" t="b">
         <v>1</v>
@@ -13286,7 +13286,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:31</t>
+          <t>2026-04-26 21:20:50</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -13336,7 +13336,7 @@
         <v>168375</v>
       </c>
       <c r="L182" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M182" t="b">
         <v>1</v>
@@ -13357,7 +13357,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:33</t>
+          <t>2026-04-26 21:20:52</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -13407,7 +13407,7 @@
         <v>168375</v>
       </c>
       <c r="L183" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M183" t="b">
         <v>1</v>
@@ -13428,7 +13428,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:33</t>
+          <t>2026-04-26 21:20:52</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -13478,7 +13478,7 @@
         <v>168375</v>
       </c>
       <c r="L184" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M184" t="b">
         <v>1</v>
@@ -13499,7 +13499,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:35</t>
+          <t>2026-04-26 21:20:54</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -13549,7 +13549,7 @@
         <v>168375</v>
       </c>
       <c r="L185" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M185" t="b">
         <v>1</v>
@@ -13570,7 +13570,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:35</t>
+          <t>2026-04-26 21:20:54</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -13620,7 +13620,7 @@
         <v>168375</v>
       </c>
       <c r="L186" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M186" t="b">
         <v>1</v>
@@ -13641,7 +13641,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:37</t>
+          <t>2026-04-26 21:20:56</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -13691,7 +13691,7 @@
         <v>168375</v>
       </c>
       <c r="L187" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M187" t="b">
         <v>1</v>
@@ -13712,7 +13712,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:37</t>
+          <t>2026-04-26 21:20:56</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -13762,7 +13762,7 @@
         <v>168375</v>
       </c>
       <c r="L188" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M188" t="b">
         <v>1</v>
@@ -13783,7 +13783,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:38</t>
+          <t>2026-04-26 21:20:58</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -13833,7 +13833,7 @@
         <v>168375</v>
       </c>
       <c r="L189" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M189" t="b">
         <v>1</v>
@@ -13854,7 +13854,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:38</t>
+          <t>2026-04-26 21:20:58</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -13904,7 +13904,7 @@
         <v>168375</v>
       </c>
       <c r="L190" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M190" t="b">
         <v>1</v>
@@ -13925,7 +13925,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:40</t>
+          <t>2026-04-26 21:21:00</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -13975,7 +13975,7 @@
         <v>168375</v>
       </c>
       <c r="L191" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M191" t="b">
         <v>1</v>
@@ -13996,7 +13996,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:40</t>
+          <t>2026-04-26 21:21:00</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -14046,7 +14046,7 @@
         <v>168375</v>
       </c>
       <c r="L192" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M192" t="b">
         <v>1</v>
@@ -14067,7 +14067,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:42</t>
+          <t>2026-04-26 21:21:01</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -14117,7 +14117,7 @@
         <v>168375</v>
       </c>
       <c r="L193" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M193" t="b">
         <v>1</v>
@@ -14138,7 +14138,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:42</t>
+          <t>2026-04-26 21:21:01</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -14188,7 +14188,7 @@
         <v>168375</v>
       </c>
       <c r="L194" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M194" t="b">
         <v>1</v>
@@ -14209,7 +14209,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:44</t>
+          <t>2026-04-26 21:21:03</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -14259,7 +14259,7 @@
         <v>168375</v>
       </c>
       <c r="L195" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M195" t="b">
         <v>1</v>
@@ -14280,7 +14280,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:44</t>
+          <t>2026-04-26 21:21:03</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -14330,7 +14330,7 @@
         <v>168375</v>
       </c>
       <c r="L196" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M196" t="b">
         <v>1</v>
@@ -14351,7 +14351,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:46</t>
+          <t>2026-04-26 21:21:05</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -14401,7 +14401,7 @@
         <v>168375</v>
       </c>
       <c r="L197" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M197" t="b">
         <v>1</v>
@@ -14422,7 +14422,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:46</t>
+          <t>2026-04-26 21:21:05</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -14472,7 +14472,7 @@
         <v>168375</v>
       </c>
       <c r="L198" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M198" t="b">
         <v>1</v>
@@ -14493,7 +14493,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:48</t>
+          <t>2026-04-26 21:21:07</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -14543,7 +14543,7 @@
         <v>168375</v>
       </c>
       <c r="L199" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M199" t="b">
         <v>1</v>
@@ -14564,7 +14564,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:48</t>
+          <t>2026-04-26 21:21:07</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -14614,7 +14614,7 @@
         <v>168375</v>
       </c>
       <c r="L200" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M200" t="b">
         <v>1</v>
@@ -14635,7 +14635,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:49</t>
+          <t>2026-04-26 21:21:09</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -14698,7 +14698,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:50</t>
+          <t>2026-04-26 21:21:10</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -14761,7 +14761,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:51</t>
+          <t>2026-04-26 21:21:10</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -14824,7 +14824,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:52</t>
+          <t>2026-04-26 21:21:12</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -14887,7 +14887,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:55</t>
+          <t>2026-04-26 21:21:14</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -14950,7 +14950,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:56</t>
+          <t>2026-04-26 21:21:16</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -15013,7 +15013,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-04-26 00:30:58</t>
+          <t>2026-04-26 21:21:17</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -15076,7 +15076,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:00</t>
+          <t>2026-04-26 21:21:19</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -15139,7 +15139,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:02</t>
+          <t>2026-04-26 21:21:21</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -15202,7 +15202,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:04</t>
+          <t>2026-04-26 21:21:23</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -15265,7 +15265,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:06</t>
+          <t>2026-04-26 21:21:25</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -15328,7 +15328,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:07</t>
+          <t>2026-04-26 21:21:27</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -15391,7 +15391,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:09</t>
+          <t>2026-04-26 21:21:29</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -15454,7 +15454,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:11</t>
+          <t>2026-04-26 21:21:31</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -15517,7 +15517,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:13</t>
+          <t>2026-04-26 21:21:33</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -15580,7 +15580,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:15</t>
+          <t>2026-04-26 21:21:34</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -15643,7 +15643,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:16</t>
+          <t>2026-04-26 21:21:36</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -15706,7 +15706,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:17</t>
+          <t>2026-04-26 21:21:36</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -15777,7 +15777,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:17</t>
+          <t>2026-04-26 21:21:36</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -15848,7 +15848,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:19</t>
+          <t>2026-04-26 21:21:38</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -15919,7 +15919,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:19</t>
+          <t>2026-04-26 21:21:38</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -15990,7 +15990,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:20</t>
+          <t>2026-04-26 21:21:40</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -16061,7 +16061,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:20</t>
+          <t>2026-04-26 21:21:40</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -16132,7 +16132,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:22</t>
+          <t>2026-04-26 21:21:42</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -16203,7 +16203,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:22</t>
+          <t>2026-04-26 21:21:42</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -16274,7 +16274,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:24</t>
+          <t>2026-04-26 21:21:44</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -16345,7 +16345,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:24</t>
+          <t>2026-04-26 21:21:44</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -16416,7 +16416,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:26</t>
+          <t>2026-04-26 21:21:46</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -16487,7 +16487,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:28</t>
+          <t>2026-04-26 21:21:48</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -16558,7 +16558,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:30</t>
+          <t>2026-04-26 21:21:50</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -16629,7 +16629,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:30</t>
+          <t>2026-04-26 21:21:50</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -16700,7 +16700,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:32</t>
+          <t>2026-04-26 21:21:52</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -16771,7 +16771,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:32</t>
+          <t>2026-04-26 21:21:52</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -16842,7 +16842,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:34</t>
+          <t>2026-04-26 21:21:54</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -16913,7 +16913,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:34</t>
+          <t>2026-04-26 21:21:54</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -16984,7 +16984,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:36</t>
+          <t>2026-04-26 21:21:56</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -17055,7 +17055,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:36</t>
+          <t>2026-04-26 21:21:56</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:38</t>
+          <t>2026-04-26 21:21:58</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -17197,7 +17197,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:38</t>
+          <t>2026-04-26 21:21:58</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -17268,7 +17268,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:40</t>
+          <t>2026-04-26 21:22:00</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -17339,7 +17339,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:42</t>
+          <t>2026-04-26 21:22:02</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -17410,7 +17410,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:43</t>
+          <t>2026-04-26 21:22:03</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -17460,7 +17460,7 @@
         <v>222100</v>
       </c>
       <c r="L242" t="n">
-        <v>150.31</v>
+        <v>150.3</v>
       </c>
       <c r="M242" t="b">
         <v>0</v>
@@ -17481,7 +17481,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:45</t>
+          <t>2026-04-26 21:22:05</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -17528,7 +17528,7 @@
         </is>
       </c>
       <c r="K243" t="n">
-        <v>230055</v>
+        <v>230064</v>
       </c>
       <c r="L243" t="n">
         <v>155.69</v>
@@ -17552,7 +17552,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:45</t>
+          <t>2026-04-26 21:22:05</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -17623,7 +17623,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:45</t>
+          <t>2026-04-26 21:22:05</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -17694,7 +17694,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:47</t>
+          <t>2026-04-26 21:22:07</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -17765,7 +17765,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:47</t>
+          <t>2026-04-26 21:22:07</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -17836,7 +17836,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:49</t>
+          <t>2026-04-26 21:22:09</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -17907,7 +17907,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:49</t>
+          <t>2026-04-26 21:22:09</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -17978,7 +17978,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:50</t>
+          <t>2026-04-26 21:22:11</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -18049,7 +18049,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:50</t>
+          <t>2026-04-26 21:22:11</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -18120,7 +18120,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:52</t>
+          <t>2026-04-26 21:22:13</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -18191,7 +18191,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:52</t>
+          <t>2026-04-26 21:22:13</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -18262,7 +18262,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:54</t>
+          <t>2026-04-26 21:22:15</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -18333,7 +18333,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:54</t>
+          <t>2026-04-26 21:22:15</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -18404,7 +18404,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:56</t>
+          <t>2026-04-26 21:22:17</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -18475,7 +18475,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:56</t>
+          <t>2026-04-26 21:22:17</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -18546,7 +18546,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:58</t>
+          <t>2026-04-26 21:22:18</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -18617,7 +18617,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>2026-04-26 00:31:58</t>
+          <t>2026-04-26 21:22:18</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -18688,7 +18688,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:00</t>
+          <t>2026-04-26 21:22:20</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -18759,7 +18759,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:00</t>
+          <t>2026-04-26 21:22:20</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -18830,7 +18830,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:02</t>
+          <t>2026-04-26 21:22:22</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -18901,7 +18901,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:02</t>
+          <t>2026-04-26 21:22:22</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -18972,7 +18972,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:03</t>
+          <t>2026-04-26 21:22:24</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -19043,7 +19043,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:03</t>
+          <t>2026-04-26 21:22:24</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -19114,7 +19114,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:05</t>
+          <t>2026-04-26 21:22:26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -19185,7 +19185,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:05</t>
+          <t>2026-04-26 21:22:26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -19256,7 +19256,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:07</t>
+          <t>2026-04-26 21:22:28</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -19327,7 +19327,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:07</t>
+          <t>2026-04-26 21:22:28</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -19398,7 +19398,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:09</t>
+          <t>2026-04-26 21:22:30</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -19469,7 +19469,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:09</t>
+          <t>2026-04-26 21:22:30</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -19540,7 +19540,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:10</t>
+          <t>2026-04-26 21:22:32</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -19590,7 +19590,7 @@
         <v>204400</v>
       </c>
       <c r="L272" t="n">
-        <v>138.33</v>
+        <v>138.32</v>
       </c>
       <c r="M272" t="b">
         <v>0</v>
@@ -19611,7 +19611,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:11</t>
+          <t>2026-04-26 21:22:32</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -19661,7 +19661,7 @@
         <v>168375</v>
       </c>
       <c r="L273" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M273" t="b">
         <v>1</v>
@@ -19682,7 +19682,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:11</t>
+          <t>2026-04-26 21:22:32</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -19732,7 +19732,7 @@
         <v>168375</v>
       </c>
       <c r="L274" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M274" t="b">
         <v>1</v>
@@ -19753,7 +19753,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:13</t>
+          <t>2026-04-26 21:22:34</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -19803,7 +19803,7 @@
         <v>168375</v>
       </c>
       <c r="L275" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M275" t="b">
         <v>1</v>
@@ -19824,7 +19824,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:13</t>
+          <t>2026-04-26 21:22:34</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -19874,7 +19874,7 @@
         <v>168375</v>
       </c>
       <c r="L276" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M276" t="b">
         <v>1</v>
@@ -19895,7 +19895,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:14</t>
+          <t>2026-04-26 21:22:36</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -19945,7 +19945,7 @@
         <v>168375</v>
       </c>
       <c r="L277" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M277" t="b">
         <v>1</v>
@@ -19966,7 +19966,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:14</t>
+          <t>2026-04-26 21:22:36</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -20016,7 +20016,7 @@
         <v>168375</v>
       </c>
       <c r="L278" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M278" t="b">
         <v>1</v>
@@ -20037,7 +20037,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:16</t>
+          <t>2026-04-26 21:22:38</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -20087,7 +20087,7 @@
         <v>168375</v>
       </c>
       <c r="L279" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M279" t="b">
         <v>1</v>
@@ -20108,7 +20108,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:16</t>
+          <t>2026-04-26 21:22:38</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -20158,7 +20158,7 @@
         <v>168375</v>
       </c>
       <c r="L280" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M280" t="b">
         <v>1</v>
@@ -20179,7 +20179,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:18</t>
+          <t>2026-04-26 21:22:40</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -20229,7 +20229,7 @@
         <v>168375</v>
       </c>
       <c r="L281" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M281" t="b">
         <v>1</v>
@@ -20250,7 +20250,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:18</t>
+          <t>2026-04-26 21:22:40</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -20300,7 +20300,7 @@
         <v>168375</v>
       </c>
       <c r="L282" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M282" t="b">
         <v>1</v>
@@ -20321,7 +20321,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:20</t>
+          <t>2026-04-26 21:22:42</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -20371,7 +20371,7 @@
         <v>168375</v>
       </c>
       <c r="L283" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M283" t="b">
         <v>1</v>
@@ -20392,7 +20392,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:20</t>
+          <t>2026-04-26 21:22:42</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -20442,7 +20442,7 @@
         <v>168375</v>
       </c>
       <c r="L284" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M284" t="b">
         <v>1</v>
@@ -20463,7 +20463,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:22</t>
+          <t>2026-04-26 21:22:43</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -20513,7 +20513,7 @@
         <v>168375</v>
       </c>
       <c r="L285" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M285" t="b">
         <v>1</v>
@@ -20534,7 +20534,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:22</t>
+          <t>2026-04-26 21:22:43</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -20584,7 +20584,7 @@
         <v>168375</v>
       </c>
       <c r="L286" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M286" t="b">
         <v>1</v>
@@ -20605,7 +20605,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:24</t>
+          <t>2026-04-26 21:22:45</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -20655,7 +20655,7 @@
         <v>168375</v>
       </c>
       <c r="L287" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M287" t="b">
         <v>1</v>
@@ -20676,7 +20676,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:24</t>
+          <t>2026-04-26 21:22:45</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -20726,7 +20726,7 @@
         <v>168375</v>
       </c>
       <c r="L288" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M288" t="b">
         <v>1</v>
@@ -20747,7 +20747,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:26</t>
+          <t>2026-04-26 21:22:47</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -20797,7 +20797,7 @@
         <v>168375</v>
       </c>
       <c r="L289" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M289" t="b">
         <v>1</v>
@@ -20818,7 +20818,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:26</t>
+          <t>2026-04-26 21:22:47</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -20868,7 +20868,7 @@
         <v>168375</v>
       </c>
       <c r="L290" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M290" t="b">
         <v>1</v>
@@ -20889,7 +20889,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:27</t>
+          <t>2026-04-26 21:22:49</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -20939,7 +20939,7 @@
         <v>168375</v>
       </c>
       <c r="L291" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M291" t="b">
         <v>1</v>
@@ -20960,7 +20960,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:27</t>
+          <t>2026-04-26 21:22:49</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -21010,7 +21010,7 @@
         <v>168375</v>
       </c>
       <c r="L292" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M292" t="b">
         <v>1</v>
@@ -21031,7 +21031,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:29</t>
+          <t>2026-04-26 21:22:51</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -21081,7 +21081,7 @@
         <v>168375</v>
       </c>
       <c r="L293" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M293" t="b">
         <v>1</v>
@@ -21102,7 +21102,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:29</t>
+          <t>2026-04-26 21:22:51</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -21152,7 +21152,7 @@
         <v>168375</v>
       </c>
       <c r="L294" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M294" t="b">
         <v>1</v>
@@ -21173,7 +21173,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:31</t>
+          <t>2026-04-26 21:22:53</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -21223,7 +21223,7 @@
         <v>168375</v>
       </c>
       <c r="L295" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M295" t="b">
         <v>1</v>
@@ -21244,7 +21244,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:31</t>
+          <t>2026-04-26 21:22:53</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -21294,7 +21294,7 @@
         <v>168375</v>
       </c>
       <c r="L296" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M296" t="b">
         <v>1</v>
@@ -21315,7 +21315,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:33</t>
+          <t>2026-04-26 21:22:55</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -21365,7 +21365,7 @@
         <v>168375</v>
       </c>
       <c r="L297" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M297" t="b">
         <v>1</v>
@@ -21386,7 +21386,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:33</t>
+          <t>2026-04-26 21:22:55</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -21436,7 +21436,7 @@
         <v>168375</v>
       </c>
       <c r="L298" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M298" t="b">
         <v>1</v>
@@ -21457,7 +21457,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:35</t>
+          <t>2026-04-26 21:22:57</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -21507,7 +21507,7 @@
         <v>168375</v>
       </c>
       <c r="L299" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M299" t="b">
         <v>1</v>
@@ -21528,7 +21528,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:35</t>
+          <t>2026-04-26 21:22:57</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -21578,7 +21578,7 @@
         <v>168375</v>
       </c>
       <c r="L300" t="n">
-        <v>113.95</v>
+        <v>113.94</v>
       </c>
       <c r="M300" t="b">
         <v>1</v>
@@ -21599,7 +21599,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:36</t>
+          <t>2026-04-26 21:22:58</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -21662,7 +21662,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:37</t>
+          <t>2026-04-26 21:22:58</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -21725,7 +21725,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:37</t>
+          <t>2026-04-26 21:22:59</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -21788,7 +21788,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:39</t>
+          <t>2026-04-26 21:23:00</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -21851,7 +21851,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:41</t>
+          <t>2026-04-26 21:23:02</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -21914,7 +21914,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:42</t>
+          <t>2026-04-26 21:23:04</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -21977,7 +21977,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:44</t>
+          <t>2026-04-26 21:23:06</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -22040,7 +22040,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:46</t>
+          <t>2026-04-26 21:23:08</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -22103,7 +22103,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:48</t>
+          <t>2026-04-26 21:23:10</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:50</t>
+          <t>2026-04-26 21:23:12</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -22229,7 +22229,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:52</t>
+          <t>2026-04-26 21:23:14</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -22292,7 +22292,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:53</t>
+          <t>2026-04-26 21:23:16</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -22355,7 +22355,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:55</t>
+          <t>2026-04-26 21:23:18</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -22418,7 +22418,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:57</t>
+          <t>2026-04-26 21:23:20</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -22481,7 +22481,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>2026-04-26 00:32:59</t>
+          <t>2026-04-26 21:23:21</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -22544,7 +22544,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2026-04-26 00:33:01</t>
+          <t>2026-04-26 21:23:23</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -22607,7 +22607,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2026-04-26 00:33:02</t>
+          <t>2026-04-26 21:23:25</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
